--- a/output/template/公共接口模板.xlsx
+++ b/output/template/公共接口模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/ForkRunner/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8CDFF67-1C66-0B42-8AF7-1F13BBFEF99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDC314-D09F-AE4F-8311-CAED40A14389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35640" yWindow="2560" windowWidth="39380" windowHeight="23160" xr2:uid="{4AE9EA50-A92F-4A4E-A8A1-714B71A0A157}"/>
+    <workbookView xWindow="36000" yWindow="2560" windowWidth="39380" windowHeight="23160" xr2:uid="{4AE9EA50-A92F-4A4E-A8A1-714B71A0A157}"/>
   </bookViews>
   <sheets>
     <sheet name="模板" sheetId="1" r:id="rId1"/>
@@ -55,12 +55,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、默认只读取第一个sheet，其他sheet不读；
-2、表红字段必输，其他字段非必输，请按需填写；
-3、变量、提取、断言规则中每行结尾的分号为英文分号；</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>类型</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -233,6 +227,12 @@
 2、当匹配规则等于为空/不为空：
 （1）断言名称1:断言对象:断言表达式1:匹配规则;
 （2）断言名称2:断言对象:断言表达式2:匹配规则;</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、默认只读取第一个sheet，其他sheet不读；
+2、标红字段必输，其他字段非必输，请按需填写；
+3、变量、提取、断言规则中每行结尾的分号为英文分号；</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -415,26 +415,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -768,81 +768,81 @@
   <sheetData>
     <row r="1" spans="1:14" ht="30" customHeight="1">
       <c r="A1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="14" t="s">
+    </row>
+    <row r="2" spans="1:14" s="6" customFormat="1" ht="196" customHeight="1">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="6" customFormat="1" ht="196" customHeight="1">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="M2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2" s="15"/>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" ht="30" customHeight="1">
       <c r="A3" s="2"/>
@@ -875,41 +875,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="199" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
+      <c r="A1" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="12"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3" spans="1:3" ht="204" customHeight="1">
+      <c r="A3" s="13" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="204" customHeight="1">
-      <c r="A3" s="9" t="s">
-        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="81">
+      <c r="A4" s="14"/>
+      <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="81">
-      <c r="A4" s="10"/>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>10</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="297">
@@ -917,30 +917,30 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="162">
+      <c r="A6" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="162">
-      <c r="A6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="297">
+      <c r="A7" s="14"/>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="297">
-      <c r="A7" s="10"/>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:3">

--- a/output/template/公共接口模板.xlsx
+++ b/output/template/公共接口模板.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yangkai/ProjectWorkspace/ForkRunner/output/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DBDC314-D09F-AE4F-8311-CAED40A14389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001AE654-22CF-9545-8EA6-357347238C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36000" yWindow="2560" windowWidth="39380" windowHeight="23160" xr2:uid="{4AE9EA50-A92F-4A4E-A8A1-714B71A0A157}"/>
+    <workbookView xWindow="40880" yWindow="2560" windowWidth="39380" windowHeight="23160" xr2:uid="{4AE9EA50-A92F-4A4E-A8A1-714B71A0A157}"/>
   </bookViews>
   <sheets>
-    <sheet name="模板" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="帮助" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
@@ -418,6 +418,9 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -431,9 +434,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -806,7 +806,7 @@
       <c r="M1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="N1" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -875,11 +875,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="199" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="13"/>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7" t="s">
@@ -893,7 +893,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" ht="204" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -904,7 +904,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" ht="81">
-      <c r="A4" s="14"/>
+      <c r="A4" s="15"/>
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
@@ -924,7 +924,7 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="162">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -935,7 +935,7 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="297">
-      <c r="A7" s="14"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
